--- a/data/dividends_info_20260303.xlsx
+++ b/data/dividends_info_20260303.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>53.34999847412109</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>1.312090009411255</v>
+        <v>1.351351371254812</v>
       </c>
       <c r="J2" t="n">
         <v>349</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>22.6299991607666</v>
+        <v>21.90999984741211</v>
       </c>
       <c r="I3" t="n">
-        <v>3.756076144596754</v>
+        <v>3.879507101413318</v>
       </c>
       <c r="J3" t="n">
         <v>111</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>78.58000183105469</v>
+        <v>74.19999694824219</v>
       </c>
       <c r="I4" t="n">
-        <v>1.323491951853065</v>
+        <v>1.401617308320708</v>
       </c>
       <c r="J4" t="n">
         <v>76</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>53.34999847412109</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I5" t="n">
-        <v>4.12371145814966</v>
+        <v>4.247104309657982</v>
       </c>
       <c r="J5" t="n">
         <v>76</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>20.04000091552734</v>
+        <v>19.44000053405762</v>
       </c>
       <c r="I6" t="n">
-        <v>3.942115588367535</v>
+        <v>4.063785896589722</v>
       </c>
       <c r="J6" t="n">
         <v>76</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5.605000019073486</v>
+        <v>5.324999809265137</v>
       </c>
       <c r="I7" t="n">
-        <v>3.389830496939182</v>
+        <v>3.5680752451749</v>
       </c>
       <c r="J7" t="n">
         <v>76</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>56.58000183105469</v>
+        <v>52.91999816894531</v>
       </c>
       <c r="I8" t="n">
-        <v>2.474372489736455</v>
+        <v>2.645502737038174</v>
       </c>
       <c r="J8" t="n">
         <v>76</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>23.23999977111816</v>
+        <v>22.79999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>2.581755619230506</v>
+        <v>2.631579035426994</v>
       </c>
       <c r="J9" t="n">
         <v>76</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>8.920000076293945</v>
+        <v>8.579999923706055</v>
       </c>
       <c r="I10" t="n">
-        <v>5.723094121453203</v>
+        <v>5.949883502790219</v>
       </c>
       <c r="J10" t="n">
         <v>62</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>19.20000076293945</v>
+        <v>18.79999923706055</v>
       </c>
       <c r="I11" t="n">
-        <v>3.906249844779577</v>
+        <v>3.989361864023487</v>
       </c>
       <c r="J11" t="n">
         <v>62</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>4.135000228881836</v>
+        <v>3.970000028610229</v>
       </c>
       <c r="I12" t="n">
-        <v>3.62756932762159</v>
+        <v>3.778337504257153</v>
       </c>
       <c r="J12" t="n">
         <v>62</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2.234999895095825</v>
+        <v>2.184999942779541</v>
       </c>
       <c r="I13" t="n">
-        <v>2.908277541427497</v>
+        <v>2.974828453190412</v>
       </c>
       <c r="J13" t="n">
         <v>55</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>6.994999885559082</v>
+        <v>6.760000228881836</v>
       </c>
       <c r="I14" t="n">
-        <v>7.147962947536731</v>
+        <v>7.396449453711106</v>
       </c>
       <c r="J14" t="n">
         <v>48</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>12.18000030517578</v>
+        <v>11.64000034332275</v>
       </c>
       <c r="I15" t="n">
-        <v>4.433497425862394</v>
+        <v>4.639175120899109</v>
       </c>
       <c r="J15" t="n">
         <v>48</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>308.2999877929688</v>
+        <v>304.7999877929688</v>
       </c>
       <c r="I16" t="n">
-        <v>1.172559242015788</v>
+        <v>1.18602366954668</v>
       </c>
       <c r="J16" t="n">
         <v>48</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>26.20000076293945</v>
+        <v>26</v>
       </c>
       <c r="I17" t="n">
-        <v>5.190839543500142</v>
+        <v>5.230769230769231</v>
       </c>
       <c r="J17" t="n">
         <v>48</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>18.07999992370605</v>
+        <v>17.10000038146973</v>
       </c>
       <c r="I18" t="n">
-        <v>3.484513289040224</v>
+        <v>3.684210444127793</v>
       </c>
       <c r="J18" t="n">
         <v>48</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>103.3499984741211</v>
+        <v>97.77999877929688</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8708272987786841</v>
+        <v>0.9204336379993476</v>
       </c>
       <c r="J19" t="n">
         <v>48</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>70.19999694824219</v>
+        <v>66.94999694824219</v>
       </c>
       <c r="I20" t="n">
-        <v>2.451282157845007</v>
+        <v>2.57027644277612</v>
       </c>
       <c r="J20" t="n">
         <v>48</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1.600000023841858</v>
+        <v>1.539999961853027</v>
       </c>
       <c r="I21" t="n">
-        <v>3.749999944120646</v>
+        <v>3.896103992613359</v>
       </c>
       <c r="J21" t="n">
         <v>41</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20.3700008392334</v>
+        <v>20.04000091552734</v>
       </c>
       <c r="I22" t="n">
-        <v>1.276386790810681</v>
+        <v>1.297405130348809</v>
       </c>
       <c r="J22" t="n">
         <v>20</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>28.17000007629395</v>
+        <v>27.1200008392334</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3194888170260894</v>
+        <v>0.3318583968102268</v>
       </c>
       <c r="J23" t="n">
         <v>20</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>53.34999847412109</v>
+        <v>51.79999923706055</v>
       </c>
       <c r="I24" t="n">
-        <v>1.218369294453308</v>
+        <v>1.25482627330804</v>
       </c>
       <c r="J24" t="n">
         <v>-8</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1.600000023841858</v>
+        <v>1.559999942779541</v>
       </c>
       <c r="I25" t="n">
-        <v>3.749999944120646</v>
+        <v>3.846153987229934</v>
       </c>
       <c r="J25" t="n">
         <v>-22</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.1770000010728836</v>
+        <v>0.1700000017881393</v>
       </c>
       <c r="I26" t="n">
-        <v>33.89830487927155</v>
+        <v>35.29411727581883</v>
       </c>
       <c r="J26" t="n">
         <v>-29</v>
@@ -2989,7 +2989,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2999,7 +2999,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3142,7 +3142,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3186,14 +3186,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3220,14 +3220,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3244,7 +3244,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3414,7 +3414,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>CULTI Milano S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3431,7 +3431,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>CULTI Milano S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3465,7 +3465,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Impianti S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3482,7 +3482,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3499,7 +3499,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3509,14 +3509,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>Impianti S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3526,14 +3526,14 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3543,14 +3543,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -3560,14 +3560,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3577,14 +3577,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3618,7 +3618,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3669,7 +3669,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3679,14 +3679,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3703,7 +3703,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3713,14 +3713,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3737,7 +3737,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3754,7 +3754,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3764,14 +3764,14 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3788,7 +3788,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3805,7 +3805,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3832,14 +3832,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3856,7 +3856,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3866,14 +3866,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3890,7 +3890,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3900,14 +3900,14 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3924,7 +3924,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3934,14 +3934,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3958,7 +3958,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3968,14 +3968,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3985,14 +3985,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4009,7 +4009,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -4043,7 +4043,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4077,7 +4077,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4094,7 +4094,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4104,14 +4104,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4121,14 +4121,14 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4138,14 +4138,14 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4162,7 +4162,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4179,7 +4179,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4196,7 +4196,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4240,14 +4240,14 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4264,7 +4264,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4281,7 +4281,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4298,7 +4298,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4315,7 +4315,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4332,7 +4332,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4376,14 +4376,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4400,7 +4400,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4410,14 +4410,14 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4427,14 +4427,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4451,7 +4451,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4468,7 +4468,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4478,14 +4478,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4495,14 +4495,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4519,7 +4519,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4529,14 +4529,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4546,14 +4546,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4563,14 +4563,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4587,7 +4587,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4597,14 +4597,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4621,7 +4621,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4638,7 +4638,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4655,7 +4655,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4665,14 +4665,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>NEXT RE SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4689,7 +4689,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4706,7 +4706,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4723,7 +4723,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>NEXT RE SIIQ S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4791,7 +4791,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>POWERSOFT S.p.A.</t>
+          <t>Ubaldi Costruzioni S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4808,7 +4808,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4842,7 +4842,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Ubaldi Costruzioni S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4852,14 +4852,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4876,7 +4876,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Antares Vision S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4893,7 +4893,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4910,7 +4910,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4920,14 +4920,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>POWERSOFT S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4944,7 +4944,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Antares Vision S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4961,7 +4961,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4978,7 +4978,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4995,7 +4995,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5012,7 +5012,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -5029,7 +5029,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>Friends S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5063,7 +5063,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5080,7 +5080,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5097,7 +5097,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5114,7 +5114,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Friends S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5148,7 +5148,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5165,7 +5165,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5182,7 +5182,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5199,7 +5199,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5267,7 +5267,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5277,14 +5277,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5301,7 +5301,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5318,7 +5318,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Egomnia S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5328,14 +5328,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>Egomnia S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5352,7 +5352,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5369,7 +5369,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Braga Moro Sistemi di Energia S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5386,7 +5386,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5403,7 +5403,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5413,14 +5413,14 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5437,7 +5437,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5471,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Braga Moro Sistemi di Energia S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5488,7 +5488,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5505,7 +5505,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5515,14 +5515,14 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5532,14 +5532,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5556,7 +5556,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5573,7 +5573,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5617,14 +5617,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5641,7 +5641,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5658,7 +5658,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5692,7 +5692,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5709,7 +5709,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>CREACTIVES GROUP S.p.A.</t>
+          <t>Confinvest F.L. S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5719,14 +5719,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>CREACTIVES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5736,14 +5736,14 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5777,7 +5777,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5787,14 +5787,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Confinvest F.L. S.p.A.</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5811,7 +5811,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5821,14 +5821,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5845,7 +5845,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -5879,7 +5879,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5889,14 +5889,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5930,7 +5930,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5940,14 +5940,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>KME Group S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5957,14 +5957,14 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5981,7 +5981,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5998,7 +5998,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6015,7 +6015,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6025,14 +6025,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6042,14 +6042,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6066,7 +6066,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6083,7 +6083,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6100,7 +6100,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6117,7 +6117,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6127,14 +6127,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6151,7 +6151,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6168,7 +6168,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6185,7 +6185,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6202,7 +6202,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6212,14 +6212,14 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6229,14 +6229,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6246,14 +6246,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6263,14 +6263,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6287,7 +6287,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6304,7 +6304,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>KME Group S.p.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6314,14 +6314,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6338,7 +6338,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6348,14 +6348,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6372,7 +6372,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6406,7 +6406,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6423,7 +6423,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6440,7 +6440,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6457,7 +6457,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6474,7 +6474,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6491,7 +6491,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6508,7 +6508,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6525,7 +6525,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6542,7 +6542,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6559,7 +6559,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6576,7 +6576,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6593,7 +6593,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6610,7 +6610,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ELES S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6627,7 +6627,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6644,7 +6644,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6661,7 +6661,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6671,14 +6671,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>ELES S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6695,7 +6695,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6712,7 +6712,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6729,7 +6729,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6763,7 +6763,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6780,7 +6780,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6790,14 +6790,14 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6814,7 +6814,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6831,7 +6831,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6848,7 +6848,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -6865,7 +6865,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6882,7 +6882,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -6916,7 +6916,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -6933,7 +6933,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -6943,14 +6943,14 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -6960,14 +6960,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -6984,7 +6984,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7001,7 +7001,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7018,7 +7018,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7035,7 +7035,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7052,7 +7052,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7069,7 +7069,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7086,7 +7086,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7103,7 +7103,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7120,7 +7120,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7137,7 +7137,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7154,7 +7154,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7171,7 +7171,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7181,14 +7181,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7205,7 +7205,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7215,14 +7215,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Annual Preliminary Results</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7239,7 +7239,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -7256,7 +7256,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -7273,7 +7273,7 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -7290,7 +7290,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -7358,7 +7358,7 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -7375,7 +7375,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -7392,7 +7392,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -7402,14 +7402,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -7426,7 +7426,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -7443,7 +7443,7 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -7460,7 +7460,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -7477,7 +7477,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -7511,7 +7511,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -7521,14 +7521,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -7545,7 +7545,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -7562,7 +7562,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -7579,7 +7579,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -7596,7 +7596,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -7613,7 +7613,7 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -7630,7 +7630,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -7647,7 +7647,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -7664,7 +7664,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -7674,14 +7674,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -7691,14 +7691,14 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -7732,7 +7732,7 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -7742,14 +7742,14 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -7766,7 +7766,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -7776,14 +7776,14 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -7800,7 +7800,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -7817,7 +7817,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -7834,7 +7834,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -7851,7 +7851,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -7868,7 +7868,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -7885,7 +7885,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -7902,7 +7902,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -7919,7 +7919,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -7936,7 +7936,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -7953,7 +7953,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -7970,7 +7970,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -7987,7 +7987,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -8004,7 +8004,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -8014,14 +8014,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -8038,7 +8038,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -8048,14 +8048,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>NEUROSOFT</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -8072,7 +8072,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -8089,7 +8089,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -8106,7 +8106,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -8140,7 +8140,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -8150,14 +8150,14 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -8167,14 +8167,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -8191,7 +8191,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -8208,7 +8208,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>NEUROSOFT</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -8225,7 +8225,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -8242,7 +8242,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -8259,7 +8259,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -8276,7 +8276,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -8286,14 +8286,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -8303,14 +8303,14 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -8327,7 +8327,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -8337,14 +8337,14 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -8361,7 +8361,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -8378,7 +8378,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -8388,14 +8388,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -8412,7 +8412,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -8429,7 +8429,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -8439,14 +8439,14 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -8463,7 +8463,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -8480,7 +8480,7 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -8497,7 +8497,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -8507,14 +8507,14 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -8573,104 +8573,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005418204</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-04-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-04-15</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>1.600000023841858</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3.749999944120646</v>
-      </c>
-      <c r="I2" t="n">
-        <v>41</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8681,146 +8586,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Digital Value S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>INWIT S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Reti S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STMicroelectronics N.V.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>